--- a/outputs/tables/tabla_modelos_clasicos.xlsx
+++ b/outputs/tables/tabla_modelos_clasicos.xlsx
@@ -411,10 +411,10 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>-15523.0145</v>
+        <v>-3550.655</v>
       </c>
       <c r="C2">
-        <v>-1962.8629</v>
+        <v>-1553.4064</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -422,10 +422,10 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>31052.0289</v>
+        <v>7107.31</v>
       </c>
       <c r="C3">
-        <v>3933.7259</v>
+        <v>3114.8129</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -433,10 +433,10 @@
         <v>5</v>
       </c>
       <c r="B4">
-        <v>31065.8163</v>
+        <v>7119.881</v>
       </c>
       <c r="C4">
-        <v>3952.109</v>
+        <v>3131.5741</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -444,7 +444,10 @@
         <v>6</v>
       </c>
       <c r="B5">
-        <v>0.0732</v>
+        <v>0.0507</v>
+      </c>
+      <c r="C5">
+        <v>0.0106</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/tables/tabla_modelos_clasicos.xlsx
+++ b/outputs/tables/tabla_modelos_clasicos.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Métrica</t>
   </si>
@@ -32,9 +32,6 @@
   </si>
   <si>
     <t>BIC (Bayesiano)</t>
-  </si>
-  <si>
-    <t>Pseudo R² (McFadden)</t>
   </si>
 </sst>
 </file>
@@ -392,7 +389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -439,17 +436,6 @@
         <v>3131.5741</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>0.0507</v>
-      </c>
-      <c r="C5">
-        <v>0.0106</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
